--- a/DuurzaamFundamentals.xlsx
+++ b/DuurzaamFundamentals.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerben\Google Drive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerben\Google Drive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65BB792-5797-453F-B992-8892364599C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569FC1A7-842F-4AC1-B555-DC89EF1B5510}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8700" yWindow="5565" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
     <sheet name="Blad2" sheetId="2" r:id="rId2"/>
-    <sheet name="Moningstar" sheetId="3" r:id="rId3"/>
+    <sheet name="Moningstar World" sheetId="3" r:id="rId3"/>
+    <sheet name="MorningStar EM + Small" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
   <si>
     <t>SAWD heeft zo'n 100 uitsluitingen. Lijkt wat op NT world.</t>
   </si>
@@ -146,6 +147,39 @@
   </si>
   <si>
     <t>ESG screen</t>
+  </si>
+  <si>
+    <t>Vanguard EM</t>
+  </si>
+  <si>
+    <t>Actiam</t>
+  </si>
+  <si>
+    <t>Small caps</t>
+  </si>
+  <si>
+    <t>Vanguard</t>
+  </si>
+  <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>NT EM</t>
+  </si>
+  <si>
+    <t>http://tools.morningstar.nl/nl/fundcompare/default.aspx?SecurityTokenList=F000013ON4%5D2%5D0%5DFXNLD$$ALL%7cF00000SDL5%5D2%5D0%5DFXNLD$$ALL&amp;CurrencyId=EUR&amp;LanguageId=nl-NL</t>
+  </si>
+  <si>
+    <t>http://tools.morningstar.nl/nl/fundcompare/default.aspx?SecurityTokenList=F00000WL32%5D2%5D0%5DFXNLD$$ALL%7cF00000S7JA%5D2%5D0%5DFXNLD$$ALL%7cF00000XXHS%5D2%5D0%5DFXNLD$$ALL%7cF0GBR04B1D%5D2%5D0%5DFXNLD$$ALL&amp;CurrencyId=EUR&amp;LanguageId=nl-NL</t>
+  </si>
+  <si>
+    <t>SPDR</t>
+  </si>
+  <si>
+    <t>optimized</t>
+  </si>
+  <si>
+    <t>EDMW zat hier veel in cash (1,39%)</t>
   </si>
 </sst>
 </file>
@@ -772,7 +806,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE07B661-A5E4-4BF6-936C-1F4550AD22FB}">
-  <dimension ref="B2:G17"/>
+  <dimension ref="B2:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
@@ -869,6 +903,26 @@
         <v>27</v>
       </c>
     </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>44168</v>
+      </c>
+      <c r="C7">
+        <v>22.04</v>
+      </c>
+      <c r="D7">
+        <v>22.84</v>
+      </c>
+      <c r="E7">
+        <v>22.83</v>
+      </c>
+      <c r="F7">
+        <v>23.3</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -952,6 +1006,23 @@
       </c>
       <c r="F17">
         <v>3.09</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>44168</v>
+      </c>
+      <c r="C18">
+        <v>2.76</v>
+      </c>
+      <c r="D18">
+        <v>2.83</v>
+      </c>
+      <c r="E18">
+        <v>2.79</v>
+      </c>
+      <c r="F18">
+        <v>3.34</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE68F06-4D51-46E4-B012-EFE246D61B74}">
-  <dimension ref="B2:H41"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
@@ -976,7 +1047,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
@@ -988,7 +1059,7 @@
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1001,7 +1072,7 @@
       </c>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>32</v>
       </c>
@@ -1014,7 +1085,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>33</v>
       </c>
@@ -1027,7 +1098,7 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
@@ -1040,7 +1111,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
@@ -1055,8 +1126,12 @@
         <f>E7-$E$3</f>
         <v>-9.5834291676250016E-4</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <f>C5-C7</f>
+        <v>-0.44999999999999929</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1072,7 +1147,7 @@
         <v>-1.302511904545306E-3</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
@@ -1088,7 +1163,7 @@
         <v>-8.494560083722319E-5</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
@@ -1101,14 +1176,14 @@
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="6"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
@@ -1124,7 +1199,7 @@
         <v>-2.9848227731630178E-3</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1344,4 +1419,218 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId31"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9720CF81-7841-4B7B-9E97-7ADF6439603E}">
+  <dimension ref="B2:G27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1">
+        <v>44104</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>15.74</v>
+      </c>
+      <c r="D3" s="3">
+        <f>100/C3</f>
+        <v>6.3532401524777633</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>16.28</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" ref="D4:D5" si="0">100/C4</f>
+        <v>6.142506142506142</v>
+      </c>
+      <c r="E4" s="3">
+        <f>D4-$D$3</f>
+        <v>-0.21073400997162128</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5">
+        <v>16.18</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>6.1804697156983934</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" ref="E5:E6" si="1">D5-$D$3</f>
+        <v>-0.17277043677936987</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>-6.3532401524777633</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1">
+        <v>44104</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>18.16</v>
+      </c>
+      <c r="D20" s="3">
+        <f>100/C20</f>
+        <v>5.5066079295154182</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>18.38</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" ref="D21:D22" si="2">100/C21</f>
+        <v>5.4406964091403704</v>
+      </c>
+      <c r="E21" s="3">
+        <f>D21-$D$20</f>
+        <v>-6.5911520375047772E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22">
+        <v>18.43</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" si="2"/>
+        <v>5.4259359739555073</v>
+      </c>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27">
+        <v>1.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{64EBFB08-5612-4E6C-8607-D1D4B3867FEA}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{60E42200-1DDF-4AD7-973B-DA067649C882}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{C3EA7A07-0FD7-451A-B8D0-3C6F40B396D9}"/>
+    <hyperlink ref="B20" r:id="rId4" xr:uid="{E6FA7D5F-13B4-47CE-8769-096C35A5C453}"/>
+    <hyperlink ref="B21" r:id="rId5" xr:uid="{CC5CA74C-1E10-45CC-A205-DDDE75274424}"/>
+    <hyperlink ref="B4" r:id="rId6" xr:uid="{DB211212-BB7F-4E7D-BBA0-A04124038990}"/>
+    <hyperlink ref="G19" r:id="rId7" xr:uid="{4D71DF0B-DFD2-4B83-AEF7-1308C1ABF73E}"/>
+    <hyperlink ref="G5" r:id="rId8" xr:uid="{DB7A0C6C-F083-4C5F-858D-86028563ED3F}"/>
+    <hyperlink ref="B22" r:id="rId9" xr:uid="{E95DCC2D-9FC7-41DA-98C1-648F25228C14}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+</worksheet>
 </file>